--- a/public/templates/client_import_template.xlsx
+++ b/public/templates/client_import_template.xlsx
@@ -452,7 +452,7 @@
         <v>poolNotes</v>
       </c>
       <c r="R1" t="str">
-        <v>poolType</v>
+        <v>hasSaltSystem</v>
       </c>
       <c r="S1" t="str">
         <v>poolState</v>
@@ -526,7 +526,7 @@
         <v>notes</v>
       </c>
       <c r="R2" t="str">
-        <v>Chlorine</v>
+        <v>FALSE (Type TRUE or FALSE)</v>
       </c>
       <c r="S2" t="str">
         <v>FL</v>
